--- a/25-11-pdf-Analyzer/begriffe_hierarchie.xlsx
+++ b/25-11-pdf-Analyzer/begriffe_hierarchie.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stufe 2</t>
+          <t>Stufe 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wahl, Verteilung, Beteiligung, Gerechtigkeit, Gleichheit, Rechte, Zugang, Macht, Vertretung, Mitsprache</t>
+          <t>Recht, Staat, Stimme, Regeln, Macht, Gruppe, Ordnung, Freiheit, Verwaltung, Gesellschaft, System, Wert, Entscheidung</t>
         </is>
       </c>
     </row>
@@ -470,46 +470,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stufe 3</t>
+          <t>Stufe 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wahlsystem, Stimmenverteilung, Repräsentation, Machtverteilung, Diskriminierungsschutz, Menschenrechtsverletzung, Partizipation, Gewaltenteilung, Rechtsstaatlichkeit</t>
+          <t>Wahl, Verteilung, Beteiligung, Rechte, Mitsprache, Bürger, Gesetz, Volk, Pflicht, Zusammenleben, Entscheidung, Regierung, Politik</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Natürliche Umwelt und Ressourcen</t>
+          <t>Politik, Demokratie und Menschenrechte</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stufe 1</t>
+          <t>Stufe 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Natur, Erde, Leben, Stoff, Tier, Pflanze, Wetter</t>
+          <t>Gerechtigkeit, Mitsprache, Gleichheit, Zugang, Beteiligung, Grundrechte, Schutz, Teilhabe, Minderheit, Mehrheit, Demokratie, Frieden, Entscheidungsprozess</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Natürliche Umwelt und Ressourcen</t>
+          <t>Politik, Demokratie und Menschenrechte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stufe 2</t>
+          <t>Stufe 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Umwelt, Klima, Energie, Wasser, Wald, Arten, Natur, Ressourcen, Verbrauch, Emissionen, Schutz, Recycling, Fläche, Rohstoffe</t>
+          <t>Wahlsystem, Stimmenverteilung, Repräsentation, Machtverteilung, Diskriminierungsschutz, Menschenrechtsverletzung, Partizipationsverfahren, Gewaltenteilung, Rechtsstaatlichkeit, Bildungszugang, Verfassungsrecht, Mindeststandards</t>
         </is>
       </c>
     </row>
@@ -521,19 +521,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stufe 3</t>
+          <t>Stufe 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biodiversität, Ökosystem, ökologischer Fußabdruck, Regenerationsrate, Nachhaltigkeit, Klimawandel, erneuerbare Energien, CO2, Treibhausgas</t>
+          <t>Natur, Erde, Leben, Stoff, Tier, Pflanze, Wetter, Boden, Berg, Wasser, Wald, Wiese, Luft, Rohstoff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Geschlechter und Gleichstellung</t>
+          <t>Natürliche Umwelt und Ressourcen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -543,14 +543,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gehalt, Lohn, Frauen, Männer, Mädchen, Jungen, Arbeitszeit, Verteilung, Berufe, Anteil, Unterschied, Familie, Ausbildung, Quote</t>
+          <t>Umwelt, Energie, Wasser, Klima, Wald, Arten, Natur, Ressourcen, Landschaft, Lebensraum, Boden, Material, Sonne, Stein</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Geschlechter und Gleichstellung</t>
+          <t>Natürliche Umwelt und Ressourcen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -560,48 +560,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lohngleichheit, Gender Pay Gap, Frauenquote, Elternzeit, Care-Arbeit, Geschlechterstereotypen, Chancengleichheit</t>
+          <t>Verbrauch, Schutz, Emissionen, Ressourcen, Nachhaltigkeit, Artenvielfalt, Kreislauf, Erneuerbarkeit, Recycling, Umweltbelastung, Naturschutz, Ökologie, Flächennutzung</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Natürliche Umwelt und Ressourcen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stufe 2</t>
+          <t>Stufe 4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ernährung, Bewegung, Versorgung, Belastung, Wohlbefinden, Prävention, Qualität, Zugang, Ausgaben, Lebensdauer, Lebenserwartung</t>
+          <t>Biodiversität, Ökosystem, ökologischer Fussabdruck, Regenerationsrate, Klimawandel, CO2-Emission, Energieverbrauch, Wasserverbrauch, Flächenverbrauch, Naturschutzgebiet, Waldanteil, Bodenerosion, Umweltindikator, Schadstoffbelastung</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gesundheit</t>
+          <t>Geschlechter und Gleichstellung</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stufe 3</t>
+          <t>Stufe 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gesundheitssystem, Krankenversicherung, Prävention, psychische Gesundheit, Ernährungssicherheit, Gesundheitsversorgung</t>
+          <t>Mann, Frau, gleich, Rolle, Mensch, Person, Gruppe, Kind, Erwachsene, Arbeit, Familie, Partner, Eltern</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Globale Entwicklung und Frieden</t>
+          <t>Geschlechter und Gleichstellung</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -611,14 +611,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Entwicklung, Verteilung, Armut, Wohlstand, Frieden, Migration, Bildung, Bevölkerung, Stadt, Land, Chancen, Zusammenarbeit, Globaler Süden</t>
+          <t>Arbeit, Anteil, Lohn, Beruf, Ausbildung, Familie, Recht, Bildung, Teilhabe, Entscheidung, Zugang, Anerkennung, Zusammenleben</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Globale Entwicklung und Frieden</t>
+          <t>Geschlechter und Gleichstellung</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -628,48 +628,48 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Entwicklungshilfe, Entwicklungsländer, Entwicklungszusammenarbeit, Konfliktprävention, Friedenssicherung, Flucht, Integration, Nord-Süd-Gefälle</t>
+          <t>Verteilung, Unterschied, Gehalt, Quote, Aufgaben, Berufswahl, Bildungschancen, Teilzeit, Vollzeit, Rollenverständnis, Chancengleichheit, Mitbestimmung, Diskriminierung</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kulturelle Identitäten und interkulturelle Verständigung</t>
+          <t>Geschlechter und Gleichstellung</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stufe 2</t>
+          <t>Stufe 4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sprache, Kultur, Vielfalt, Integration, Minderheit, Austausch, Gemeinschaft, Tradition, Kommunikation, Zusammenleben</t>
+          <t>Lohnungleichheit, Führungspositionen, Care-Arbeit, Geschlechterquote, Elternzeit, Berufseinstieg, Aufstiegschancen, Rollenstereotype, Vereinbarkeit, Betreuungsangebote, Karriereunterbrechung, Diskriminierungsschutz, paritätische Besetzung</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kulturelle Identitäten und interkulturelle Verständigung</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stufe 3</t>
+          <t>Stufe 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kulturelle Vielfalt, Multikulturalität, interkultureller Dialog, Diskriminierung, Inklusion, kulturelle Identität</t>
+          <t>Körper, Essen, Leben, Luft, Rein, Krankheit, Arzt, Medizin, Sport, Pflege, Alter, Ruhe, Nahrung, Bewegung</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wirtschaft und Konsum</t>
+          <t>Gesundheit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -679,24 +679,245 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Produktion, Konsum, Transport, Handel, Kosten, Preis, Effizienz, Lebensmittel, Regional, Verschwendung, Nutzen, Verbrauch, Kette, Schulden</t>
+          <t>Ernährung, Bewegung, Wohlbefinden, Qualität, Versorgung, Medikament, Krankheit, Hygiene, Beratung, Vorsorge, Therapie, Behandlung, Stress</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Gesundheit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stufe 3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Versorgung, Belastung, Zugang, Prävention, Umweltfaktoren, Vorsorgeuntersuchung, Gesundheitssystem, Lebensstil, Risikofaktoren, Früherkennung, Gesundheitsförderung, Ernährungsbildung, Gesundheitskompetenz</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gesundheit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stufe 4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Lebenserwartung, Krankheitsrate, Gesundheitsausgaben, Mortalitätsrate, Präventionsprogramme, Gesundheitsmonitoring, Ernährungssicherheit, Kalorienverbrauch, Bewegungsmangel, Impfrate, Medikamentenversorgung, Trinkwasserqualität, Luftverschmutzung, medizinische Grundversorgung</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Globale Entwicklung und Frieden</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Stufe 1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Welt, Land, Hilfe, Armut, Gruppe, Krieg, Frieden, Staat, Region, Nation, Gemeinschaft, Unterstützung, Handel, Zusammenarbeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Globale Entwicklung und Frieden</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Stufe 2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Entwicklung, Zusammenarbeit, Chancen, Verteilung, Frieden, Migration, Welthandel, International, Wirtschaft, Hilfsorganisation, Politik, Kommunikation, Diplomatie, Handel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Globale Entwicklung und Frieden</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Stufe 3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wohlstand, Bildung, Migration, Bevölkerung, Wirtschaftswachstum, Entwicklungshilfe, Diplomatie, Krisenregion, Flüchtlinge, Konflikte, Kooperation, Handelsbeziehungen, Friedenssicherung, globale Partnerschaft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Globale Entwicklung und Frieden</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Stufe 4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nord-Süd-Gefälle, Entwicklungsindex, Friedenssicherung, Alphabetisierungsrate, Entwicklungszusammenarbeit, Armutsbekämpfung, Bevölkerungswachstum, Migrationsbewegungen, Konfliktlösung, Wohlstandsverteilung, Ressourcenkonflikte, humanitäre Hilfe, Nachhaltigkeitsziele, Ungleichheitsindikator</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kulturelle Identitäten und interkulturelle Verständigung</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Stufe 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sprache, Gruppe, Art, Brauch, Fest, Glauben, Musik, Kunst, Essen, Kleidung, Familie, Wohnen, Tradition, Religion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kulturelle Identitäten und interkulturelle Verständigung</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stufe 2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kultur, Vielfalt, Tradition, Austausch, Religion, Gemeinschaft, Werte, Begegnung, Dialog, Heimat, Geschichte, Selbstverständnis, Zugehörigkeit, Feiertag</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kulturelle Identitäten und interkulturelle Verständigung</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stufe 3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Integration, Minderheit, Zusammenleben, Kommunikation, Verständigung, Religionsgemeinschaft, Herkunftskultur, Mehrsprachigkeit, Unterschiede, Gemeinsamkeiten, Kulturerbe, Toleranz, Kulturaustausch, Erinnerungskultur</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kulturelle Identitäten und interkulturelle Verständigung</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stufe 4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sprachenvielfalt, kulturelle Diversität, Identitätsbildung, interkulturelle Kommunikation, Migrationsgeschichte, kollektives Gedächtnis, kulturelle Aneignung, Traditionsbewusstsein, kulturelle Missverständnisse, Integrationsprogramme, Minderheitenrechte, kulturhistorisches Erbe, Kulturtransfer, Sozialisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Wirtschaft und Konsum</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Stufe 1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Geld, Ware, Tausch, Kauf, Markt, Handel, Preis, Verkauf, Arbeit, Geschäft, Leistung, Produkt, Lohn, Werbung</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Wirtschaft und Konsum</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Stufe 2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Handel, Preis, Kosten, Verbrauch, Verkauf, Regional, Angebot, Nachfrage, Qualität, Marke, Einkauf, Produktion, Hersteller, Kunde</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Wirtschaft und Konsum</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Stufe 3</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>nachhaltiger Konsum, Konsumverhalten, Produktionsbedingungen, Lieferkette, fairer Handel, Kreislaufwirtschaft, Lebensmittelverschwendung, ökologischer Fußabdruck</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Produktion, Konsum, Transport, Effizienz, Lieferkette, Verpackung, Verschwendung, Rohstoffe, Langlebigkeit, Wertschöpfung, Umweltfolgen, Vermarktung, Handelsströme, Produktionsbedingungen, Schulden</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Wirtschaft und Konsum</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Stufe 4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kreislaufwirtschaft, Lieferketten, Ressourceneffizienz, faire Handelsbeziehungen, Produktlebenszyklus, Verbraucherschutz, ökologischer Rucksack, Lebensmittelverschwendung, nachhaltiges Wirtschaftswachstum, soziale Produktionsbedingungen, Konsummuster, Regionalvermarktung, Transportwege, Wertschöpfungsketten</t>
         </is>
       </c>
     </row>
